--- a/Assets/Configs/CharacterConfig.xlsx
+++ b/Assets/Configs/CharacterConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\PCR\Assets\Configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85087C71-C312-4D32-B23B-69763C92C0C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7888A06-C534-4B73-A37F-4441310D76BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="42">
   <si>
     <t>Id</t>
   </si>
@@ -64,9 +64,6 @@
     <t>攻击范围</t>
   </si>
   <si>
-    <t>走路动画</t>
-  </si>
-  <si>
     <t>攻击动画</t>
   </si>
   <si>
@@ -127,6 +124,48 @@
   </si>
   <si>
     <t>镜华</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>跑步动画</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>入场跑步动画</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AnimStandBy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>准备动画</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>01_standBy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>07_standBy</t>
+  </si>
+  <si>
+    <t>04_standBy</t>
+  </si>
+  <si>
+    <t>01_run_gamestart</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AnimRunGameStart</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>07_run_gamestart</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>04_run_gamestart</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -474,21 +513,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
     <col min="3" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="13.75" customWidth="1"/>
-    <col min="6" max="6" width="17" customWidth="1"/>
+    <col min="6" max="6" width="18.75" customWidth="1"/>
     <col min="7" max="7" width="16.125" customWidth="1"/>
-    <col min="8" max="8" width="23.125" customWidth="1"/>
+    <col min="8" max="8" width="14.75" customWidth="1"/>
     <col min="9" max="9" width="18" customWidth="1"/>
     <col min="10" max="10" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -505,19 +544,25 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -534,24 +579,30 @@
         <v>13</v>
       </c>
       <c r="F2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I2" t="s">
         <v>14</v>
       </c>
-      <c r="G2" t="s">
+      <c r="J2" t="s">
         <v>15</v>
       </c>
-      <c r="H2" t="s">
+      <c r="K2" t="s">
         <v>16</v>
       </c>
-      <c r="I2" t="s">
-        <v>17</v>
-      </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A3">
         <v>1001</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C3">
         <v>5800</v>
@@ -563,24 +614,30 @@
         <v>200</v>
       </c>
       <c r="F3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" t="s">
         <v>18</v>
       </c>
-      <c r="G3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" t="s">
-        <v>25</v>
-      </c>
-      <c r="I3">
+      <c r="J3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K3">
         <v>1001</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A4">
         <v>1002</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C4">
         <v>4000</v>
@@ -592,24 +649,30 @@
         <v>800</v>
       </c>
       <c r="F4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G4" t="s">
+        <v>36</v>
+      </c>
+      <c r="H4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" t="s">
         <v>22</v>
       </c>
-      <c r="G4" t="s">
+      <c r="J4" t="s">
         <v>23</v>
       </c>
-      <c r="H4" t="s">
-        <v>24</v>
-      </c>
-      <c r="I4">
+      <c r="K4">
         <v>1002</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A5">
         <v>1003</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C5">
         <v>5000</v>
@@ -621,24 +684,30 @@
         <v>250</v>
       </c>
       <c r="F5" t="s">
+        <v>41</v>
+      </c>
+      <c r="G5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I5" t="s">
         <v>28</v>
       </c>
-      <c r="G5" t="s">
+      <c r="J5" t="s">
         <v>29</v>
       </c>
-      <c r="H5" t="s">
-        <v>30</v>
-      </c>
-      <c r="I5">
+      <c r="K5">
         <v>1003</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A6">
         <v>1010</v>
       </c>
       <c r="B6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C6">
         <v>1000</v>
@@ -650,24 +719,30 @@
         <v>795</v>
       </c>
       <c r="F6" t="s">
+        <v>40</v>
+      </c>
+      <c r="G6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" t="s">
         <v>22</v>
       </c>
-      <c r="G6" t="s">
+      <c r="J6" t="s">
         <v>23</v>
       </c>
-      <c r="H6" t="s">
-        <v>24</v>
-      </c>
-      <c r="I6">
+      <c r="K6">
         <v>1010</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A7">
         <v>1036</v>
       </c>
       <c r="B7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C7">
         <v>1000</v>
@@ -679,15 +754,21 @@
         <v>810</v>
       </c>
       <c r="F7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G7" t="s">
+        <v>36</v>
+      </c>
+      <c r="H7" t="s">
+        <v>21</v>
+      </c>
+      <c r="I7" t="s">
         <v>22</v>
       </c>
-      <c r="G7" t="s">
+      <c r="J7" t="s">
         <v>23</v>
       </c>
-      <c r="H7" t="s">
-        <v>24</v>
-      </c>
-      <c r="I7">
+      <c r="K7">
         <v>1036</v>
       </c>
     </row>

--- a/Assets/Configs/CharacterConfig.xlsx
+++ b/Assets/Configs/CharacterConfig.xlsx
@@ -8,19 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\PCR\Assets\Configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7888A06-C534-4B73-A37F-4441310D76BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E29FBA5-4E9B-4AD0-B0E9-948FAEECC40E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="角色配置" sheetId="1" r:id="rId1"/>
+    <sheet name="CharacterConfig" sheetId="1" r:id="rId1"/>
+    <sheet name="SkillConfig" sheetId="2" r:id="rId2"/>
+    <sheet name="SkillEffectConfig" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="83">
   <si>
     <t>Id</t>
   </si>
@@ -37,6 +39,12 @@
     <t>AttackRange</t>
   </si>
   <si>
+    <t>AnimRunGameStart</t>
+  </si>
+  <si>
+    <t>AnimStandBy</t>
+  </si>
+  <si>
     <t>AnimRun</t>
   </si>
   <si>
@@ -46,9 +54,6 @@
     <t>AnimIdle</t>
   </si>
   <si>
-    <t>SpineDataAddr</t>
-  </si>
-  <si>
     <t>角色ID</t>
   </si>
   <si>
@@ -64,13 +69,25 @@
     <t>攻击范围</t>
   </si>
   <si>
+    <t>开局跑步动画</t>
+  </si>
+  <si>
+    <t>跑步动画</t>
+  </si>
+  <si>
     <t>攻击动画</t>
   </si>
   <si>
     <t>待机动画</t>
   </si>
   <si>
-    <t>Spine地址</t>
+    <t>日和莉</t>
+  </si>
+  <si>
+    <t>01_run_gamestart</t>
+  </si>
+  <si>
+    <t>01_standBy</t>
   </si>
   <si>
     <t>01_run</t>
@@ -79,63 +96,144 @@
     <t>01_attack</t>
   </si>
   <si>
-    <t>日和莉</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>优衣</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>07_run_gamestart</t>
+  </si>
+  <si>
+    <t>07_standBy</t>
   </si>
   <si>
     <t>07_run</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>07_attack</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>07_multy_idle_standBy</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>01_multy_idle_standBy</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>怜</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>04_run_gamestart</t>
+  </si>
+  <si>
+    <t>04_standBy</t>
+  </si>
+  <si>
+    <t>04_run</t>
+  </si>
+  <si>
+    <t>04_attack</t>
   </si>
   <si>
     <t>真步</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>04_run</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>04_attack</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>04_multy_idle_standBy</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>镜华</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>跑步动画</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>入场跑步动画</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AnimStandBy</t>
+  </si>
+  <si>
+    <t>CastTime</t>
+  </si>
+  <si>
+    <t>AnimName</t>
+  </si>
+  <si>
+    <t>SoundName</t>
+  </si>
+  <si>
+    <t>技能ID</t>
+  </si>
+  <si>
+    <t>技能名称</t>
+  </si>
+  <si>
+    <t>前摇时长(秒)</t>
+  </si>
+  <si>
+    <t>技能动画名</t>
+  </si>
+  <si>
+    <t>技能音效名</t>
+  </si>
+  <si>
+    <t>SkillId</t>
+  </si>
+  <si>
+    <t>EffectIndex</t>
+  </si>
+  <si>
+    <t>EffectType</t>
+  </si>
+  <si>
+    <t>EffectTarget</t>
+  </si>
+  <si>
+    <t>SkillMulti</t>
+  </si>
+  <si>
+    <t>EffectValue</t>
+  </si>
+  <si>
+    <t>所属技能ID</t>
+  </si>
+  <si>
+    <t>效果序号(按顺序执行)</t>
+  </si>
+  <si>
+    <t>效果类型(Damage/Heal/Buff/Debuff)</t>
+  </si>
+  <si>
+    <t>目标(SingleEnemy/AllEnemies/Self/AllAllies)</t>
+  </si>
+  <si>
+    <t>攻击力倍率</t>
+  </si>
+  <si>
+    <t>附加值(固定数值)</t>
+  </si>
+  <si>
+    <t>Damage</t>
+  </si>
+  <si>
+    <t>SingleEnemy</t>
+  </si>
+  <si>
+    <t>UbSkillId</t>
+  </si>
+  <si>
+    <t>Skill1Id</t>
+  </si>
+  <si>
+    <t>Skill2Id</t>
+  </si>
+  <si>
+    <t>AttackInterval</t>
+  </si>
+  <si>
+    <t>StartSequence</t>
+  </si>
+  <si>
+    <t>LoopSequence</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UB技能id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1技能id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2技能id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>普攻间隔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AA2A1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -143,30 +241,52 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>01_standBy</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>07_standBy</t>
-  </si>
-  <si>
-    <t>04_standBy</t>
-  </si>
-  <si>
-    <t>01_run_gamestart</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AnimRunGameStart</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>07_run_gamestart</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>04_run_gamestart</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>01_idle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>07_idle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>04_idle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>启动序列</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>循环序列</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>猫咪重击</t>
+  </si>
+  <si>
+    <t>猫咪组合拳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>日和莉突击</t>
+  </si>
+  <si>
+    <t>Damage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SingleEnemy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100101_skill0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100101_skill1</t>
+  </si>
+  <si>
+    <t>100101_skill2</t>
   </si>
 </sst>
 </file>
@@ -209,8 +329,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -513,21 +634,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:P7"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="17" customWidth="1"/>
-    <col min="3" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="13.75" customWidth="1"/>
-    <col min="6" max="6" width="18.75" customWidth="1"/>
-    <col min="7" max="7" width="16.125" customWidth="1"/>
-    <col min="8" max="8" width="14.75" customWidth="1"/>
-    <col min="9" max="9" width="18" customWidth="1"/>
-    <col min="10" max="10" width="16" customWidth="1"/>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="10.5" customWidth="1"/>
+    <col min="3" max="3" width="9.25" customWidth="1"/>
+    <col min="4" max="4" width="12.75" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="19.75" customWidth="1"/>
+    <col min="7" max="8" width="16" customWidth="1"/>
+    <col min="9" max="9" width="12.625" customWidth="1"/>
+    <col min="10" max="10" width="11.875" customWidth="1"/>
+    <col min="11" max="12" width="16" customWidth="1"/>
+    <col min="13" max="13" width="11.5" customWidth="1"/>
+    <col min="14" max="14" width="16.25" customWidth="1"/>
+    <col min="15" max="15" width="15.125" customWidth="1"/>
+    <col min="16" max="16" width="14.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -544,60 +670,90 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.15">
+        <v>58</v>
+      </c>
+      <c r="L1" t="s">
+        <v>59</v>
+      </c>
+      <c r="M1" t="s">
+        <v>60</v>
+      </c>
+      <c r="N1" t="s">
+        <v>61</v>
+      </c>
+      <c r="O1" t="s">
+        <v>62</v>
+      </c>
+      <c r="P1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F2" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="G2" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="H2" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="I2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.15">
+        <v>64</v>
+      </c>
+      <c r="L2" t="s">
+        <v>65</v>
+      </c>
+      <c r="M2" t="s">
+        <v>66</v>
+      </c>
+      <c r="N2" t="s">
+        <v>67</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="P2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A3">
         <v>1001</v>
       </c>
@@ -614,30 +770,45 @@
         <v>200</v>
       </c>
       <c r="F3" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="G3" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="H3" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I3" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J3" t="s">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="K3">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.15">
+        <v>100100</v>
+      </c>
+      <c r="L3">
+        <v>100101</v>
+      </c>
+      <c r="M3">
+        <v>100102</v>
+      </c>
+      <c r="N3">
+        <v>2.2949999999999999</v>
+      </c>
+      <c r="O3" s="1">
+        <v>21</v>
+      </c>
+      <c r="P3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A4">
         <v>1002</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C4">
         <v>4000</v>
@@ -649,30 +820,27 @@
         <v>800</v>
       </c>
       <c r="F4" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="G4" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="H4" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="I4" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J4" t="s">
-        <v>23</v>
-      </c>
-      <c r="K4">
-        <v>1002</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.15">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A5">
         <v>1003</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C5">
         <v>5000</v>
@@ -684,30 +852,27 @@
         <v>250</v>
       </c>
       <c r="F5" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="G5" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="H5" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="I5" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="J5" t="s">
-        <v>29</v>
-      </c>
-      <c r="K5">
-        <v>1003</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.15">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A6">
         <v>1010</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="C6">
         <v>1000</v>
@@ -719,30 +884,27 @@
         <v>795</v>
       </c>
       <c r="F6" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="G6" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="H6" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="I6" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J6" t="s">
-        <v>23</v>
-      </c>
-      <c r="K6">
-        <v>1010</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.15">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A7">
         <v>1036</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C7">
         <v>1000</v>
@@ -754,27 +916,232 @@
         <v>810</v>
       </c>
       <c r="F7" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="G7" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="H7" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="I7" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J7" t="s">
-        <v>23</v>
-      </c>
-      <c r="K7">
-        <v>1036</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="9" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A3">
+        <v>100100</v>
+      </c>
+      <c r="B3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A4">
+        <v>100101</v>
+      </c>
+      <c r="B4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C4">
+        <v>1.125</v>
+      </c>
+      <c r="D4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A5">
+        <v>100102</v>
+      </c>
+      <c r="B5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C5">
+        <v>1.2949999999999999</v>
+      </c>
+      <c r="D5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="20.875" customWidth="1"/>
+    <col min="3" max="3" width="32.875" customWidth="1"/>
+    <col min="4" max="4" width="44.75" customWidth="1"/>
+    <col min="5" max="5" width="12.5" customWidth="1"/>
+    <col min="6" max="6" width="18.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A3">
+        <v>100100</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E3">
+        <v>2.4</v>
+      </c>
+      <c r="F3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A4">
+        <v>100101</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E4">
+        <v>1.6</v>
+      </c>
+      <c r="F4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A5">
+        <v>100102</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D5" t="s">
+        <v>57</v>
+      </c>
+      <c r="E5">
+        <v>0.6</v>
+      </c>
+      <c r="F5">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Assets/Configs/CharacterConfig.xlsx
+++ b/Assets/Configs/CharacterConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\PCR\Assets\Configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E29FBA5-4E9B-4AD0-B0E9-948FAEECC40E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13C3A08A-FA60-4B07-9B25-75EF8055832A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CharacterConfig" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="107">
   <si>
     <t>Id</t>
   </si>
@@ -147,9 +147,6 @@
     <t>技能名称</t>
   </si>
   <si>
-    <t>前摇时长(秒)</t>
-  </si>
-  <si>
     <t>技能动画名</t>
   </si>
   <si>
@@ -287,6 +284,100 @@
   </si>
   <si>
     <t>100101_skill2</t>
+  </si>
+  <si>
+    <t>AA2A1AA1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>全体治愈</t>
+  </si>
+  <si>
+    <t>花瓣射击</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>花之庇护</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100201_skill0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100201_skill1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100201_skill2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpineId</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Spine地址</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>spine_1001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>spine_1002</t>
+  </si>
+  <si>
+    <t>spine_1003</t>
+  </si>
+  <si>
+    <t>spine_1010</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>spine_1036</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>普攻音效地址</t>
+  </si>
+  <si>
+    <t>AttackSound</t>
+  </si>
+  <si>
+    <t>audio_1001_attack</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio_1002_attack</t>
+  </si>
+  <si>
+    <t>前摇时长</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio_1001_ub</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio_1001_skill1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio_1001_skill2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio_1002_ub</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio_1002_skill1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio_1002_skill2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -634,26 +725,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P7"/>
+  <dimension ref="A1:R7"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="10.5" customWidth="1"/>
-    <col min="3" max="3" width="9.25" customWidth="1"/>
-    <col min="4" max="4" width="12.75" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="19.75" customWidth="1"/>
-    <col min="7" max="8" width="16" customWidth="1"/>
+    <col min="3" max="3" width="12.625" customWidth="1"/>
+    <col min="4" max="5" width="12.75" customWidth="1"/>
+    <col min="6" max="6" width="12.625" customWidth="1"/>
+    <col min="7" max="7" width="18.625" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1"/>
     <col min="9" max="9" width="12.625" customWidth="1"/>
     <col min="10" max="10" width="11.875" customWidth="1"/>
     <col min="11" max="12" width="16" customWidth="1"/>
     <col min="13" max="13" width="11.5" customWidth="1"/>
     <col min="14" max="14" width="16.25" customWidth="1"/>
     <col min="15" max="15" width="15.125" customWidth="1"/>
-    <col min="16" max="16" width="14.125" customWidth="1"/>
+    <col min="16" max="16" width="19" customWidth="1"/>
+    <col min="17" max="17" width="14.25" customWidth="1"/>
+    <col min="18" max="18" width="13.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -661,49 +754,55 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
+        <v>57</v>
+      </c>
+      <c r="M1" t="s">
         <v>58</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>59</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>60</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q1" t="s">
         <v>61</v>
       </c>
-      <c r="O1" t="s">
+      <c r="R1" t="s">
         <v>62</v>
       </c>
-      <c r="P1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -711,224 +810,269 @@
         <v>11</v>
       </c>
       <c r="C2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D2" t="s">
         <v>12</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>13</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>14</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>15</v>
       </c>
-      <c r="G2" t="s">
-        <v>69</v>
-      </c>
       <c r="H2" t="s">
+        <v>68</v>
+      </c>
+      <c r="I2" t="s">
         <v>16</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>17</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>18</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
+        <v>63</v>
+      </c>
+      <c r="M2" t="s">
         <v>64</v>
       </c>
-      <c r="L2" t="s">
+      <c r="N2" t="s">
         <v>65</v>
       </c>
-      <c r="M2" t="s">
+      <c r="O2" t="s">
         <v>66</v>
       </c>
-      <c r="N2" t="s">
-        <v>67</v>
-      </c>
-      <c r="O2" s="1" t="s">
+      <c r="P2" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="R2" t="s">
         <v>73</v>
       </c>
-      <c r="P2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A3">
         <v>1001</v>
       </c>
       <c r="B3" t="s">
         <v>19</v>
       </c>
-      <c r="C3">
+      <c r="C3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D3">
         <v>5800</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>1580</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>200</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>20</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>21</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>22</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>23</v>
       </c>
-      <c r="J3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K3">
+      <c r="K3" t="s">
+        <v>69</v>
+      </c>
+      <c r="L3">
         <v>100100</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <v>100101</v>
       </c>
-      <c r="M3">
+      <c r="N3">
         <v>100102</v>
       </c>
-      <c r="N3">
+      <c r="O3">
         <v>2.2949999999999999</v>
       </c>
-      <c r="O3" s="1">
+      <c r="P3" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q3" s="1">
         <v>21</v>
       </c>
-      <c r="P3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="R3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A4">
         <v>1002</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
-      <c r="C4">
+      <c r="C4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D4">
         <v>4000</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>200</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>800</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>25</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>26</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>27</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>28</v>
       </c>
-      <c r="J4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="K4" t="s">
+        <v>70</v>
+      </c>
+      <c r="L4">
+        <v>100200</v>
+      </c>
+      <c r="M4">
+        <v>100201</v>
+      </c>
+      <c r="N4">
+        <v>100202</v>
+      </c>
+      <c r="O4">
+        <v>2.27</v>
+      </c>
+      <c r="P4" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q4" s="1">
+        <v>21</v>
+      </c>
+      <c r="R4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A5">
         <v>1003</v>
       </c>
       <c r="B5" t="s">
         <v>29</v>
       </c>
-      <c r="C5">
+      <c r="C5" t="s">
+        <v>93</v>
+      </c>
+      <c r="D5">
         <v>5000</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>1000</v>
       </c>
-      <c r="E5">
+      <c r="F5">
         <v>250</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>30</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>31</v>
       </c>
-      <c r="H5" t="s">
+      <c r="I5" t="s">
         <v>32</v>
       </c>
-      <c r="I5" t="s">
+      <c r="J5" t="s">
         <v>33</v>
       </c>
-      <c r="J5" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="K5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A6">
         <v>1010</v>
       </c>
       <c r="B6" t="s">
         <v>34</v>
       </c>
-      <c r="C6">
-        <v>1000</v>
+      <c r="C6" t="s">
+        <v>94</v>
       </c>
       <c r="D6">
         <v>1000</v>
       </c>
       <c r="E6">
+        <v>1000</v>
+      </c>
+      <c r="F6">
         <v>795</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>25</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>26</v>
       </c>
-      <c r="H6" t="s">
+      <c r="I6" t="s">
         <v>27</v>
       </c>
-      <c r="I6" t="s">
+      <c r="J6" t="s">
         <v>28</v>
       </c>
-      <c r="J6" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="K6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A7">
         <v>1036</v>
       </c>
       <c r="B7" t="s">
         <v>35</v>
       </c>
-      <c r="C7">
-        <v>1000</v>
+      <c r="C7" t="s">
+        <v>95</v>
       </c>
       <c r="D7">
         <v>1000</v>
       </c>
       <c r="E7">
+        <v>1000</v>
+      </c>
+      <c r="F7">
         <v>810</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>25</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
         <v>26</v>
       </c>
-      <c r="H7" t="s">
+      <c r="I7" t="s">
         <v>27</v>
       </c>
-      <c r="I7" t="s">
+      <c r="J7" t="s">
         <v>28</v>
       </c>
-      <c r="J7" t="s">
-        <v>71</v>
+      <c r="K7" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -939,10 +1083,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="9" width="14" customWidth="1"/>
+    <col min="1" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="17.75" customWidth="1"/>
+    <col min="6" max="9" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.15">
@@ -970,13 +1116,13 @@
         <v>40</v>
       </c>
       <c r="C2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D2" t="s">
         <v>41</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>42</v>
-      </c>
-      <c r="E2" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.15">
@@ -984,13 +1130,16 @@
         <v>100100</v>
       </c>
       <c r="B3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3" t="s">
-        <v>80</v>
+        <v>79</v>
+      </c>
+      <c r="E3" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.15">
@@ -998,13 +1147,16 @@
         <v>100101</v>
       </c>
       <c r="B4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C4">
         <v>1.125</v>
       </c>
       <c r="D4" t="s">
-        <v>81</v>
+        <v>80</v>
+      </c>
+      <c r="E4" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.15">
@@ -1012,13 +1164,67 @@
         <v>100102</v>
       </c>
       <c r="B5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C5">
         <v>1.2949999999999999</v>
       </c>
       <c r="D5" t="s">
-        <v>82</v>
+        <v>81</v>
+      </c>
+      <c r="E5" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A6">
+        <v>100200</v>
+      </c>
+      <c r="B6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6" t="s">
+        <v>86</v>
+      </c>
+      <c r="E6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A7">
+        <v>100201</v>
+      </c>
+      <c r="B7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C7">
+        <v>1.6</v>
+      </c>
+      <c r="D7" t="s">
+        <v>87</v>
+      </c>
+      <c r="E7" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A8">
+        <v>100202</v>
+      </c>
+      <c r="B8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C8">
+        <v>1.46</v>
+      </c>
+      <c r="D8" t="s">
+        <v>88</v>
+      </c>
+      <c r="E8" t="s">
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -1042,42 +1248,42 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" t="s">
         <v>44</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>45</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>46</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>47</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>48</v>
-      </c>
-      <c r="F1" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B2" t="s">
         <v>50</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>51</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>52</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>53</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>54</v>
-      </c>
-      <c r="F2" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.15">
@@ -1088,10 +1294,10 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D3" t="s">
         <v>78</v>
-      </c>
-      <c r="D3" t="s">
-        <v>79</v>
       </c>
       <c r="E3">
         <v>2.4</v>
@@ -1108,10 +1314,10 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D4" t="s">
         <v>56</v>
-      </c>
-      <c r="D4" t="s">
-        <v>57</v>
       </c>
       <c r="E4">
         <v>1.6</v>
@@ -1128,10 +1334,10 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D5" t="s">
         <v>56</v>
-      </c>
-      <c r="D5" t="s">
-        <v>57</v>
       </c>
       <c r="E5">
         <v>0.6</v>

--- a/Assets/Configs/CharacterConfig.xlsx
+++ b/Assets/Configs/CharacterConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\PCR\Assets\Configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13C3A08A-FA60-4B07-9B25-75EF8055832A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54C6A7DE-4681-493A-A2F5-B0E265266CBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CharacterConfig" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="136">
   <si>
     <t>Id</t>
   </si>
@@ -57,326 +57,438 @@
     <t>角色ID</t>
   </si>
   <si>
+    <t>最大HP</t>
+  </si>
+  <si>
+    <t>攻击力</t>
+  </si>
+  <si>
+    <t>攻击范围</t>
+  </si>
+  <si>
+    <t>开局跑步动画</t>
+  </si>
+  <si>
+    <t>跑步动画</t>
+  </si>
+  <si>
+    <t>攻击动画</t>
+  </si>
+  <si>
+    <t>待机动画</t>
+  </si>
+  <si>
+    <t>日和莉</t>
+  </si>
+  <si>
+    <t>01_run_gamestart</t>
+  </si>
+  <si>
+    <t>01_standBy</t>
+  </si>
+  <si>
+    <t>01_run</t>
+  </si>
+  <si>
+    <t>01_attack</t>
+  </si>
+  <si>
+    <t>优衣</t>
+  </si>
+  <si>
+    <t>07_run_gamestart</t>
+  </si>
+  <si>
+    <t>07_standBy</t>
+  </si>
+  <si>
+    <t>07_run</t>
+  </si>
+  <si>
+    <t>07_attack</t>
+  </si>
+  <si>
+    <t>怜</t>
+  </si>
+  <si>
+    <t>04_run_gamestart</t>
+  </si>
+  <si>
+    <t>04_standBy</t>
+  </si>
+  <si>
+    <t>04_run</t>
+  </si>
+  <si>
+    <t>04_attack</t>
+  </si>
+  <si>
+    <t>真步</t>
+  </si>
+  <si>
+    <t>镜华</t>
+  </si>
+  <si>
+    <t>CastTime</t>
+  </si>
+  <si>
+    <t>AnimName</t>
+  </si>
+  <si>
+    <t>SoundName</t>
+  </si>
+  <si>
+    <t>技能ID</t>
+  </si>
+  <si>
+    <t>技能名称</t>
+  </si>
+  <si>
+    <t>技能动画名</t>
+  </si>
+  <si>
+    <t>技能音效名</t>
+  </si>
+  <si>
+    <t>SkillId</t>
+  </si>
+  <si>
+    <t>EffectIndex</t>
+  </si>
+  <si>
+    <t>EffectType</t>
+  </si>
+  <si>
+    <t>EffectTarget</t>
+  </si>
+  <si>
+    <t>SkillMulti</t>
+  </si>
+  <si>
+    <t>EffectValue</t>
+  </si>
+  <si>
+    <t>所属技能ID</t>
+  </si>
+  <si>
+    <t>效果序号(按顺序执行)</t>
+  </si>
+  <si>
+    <t>效果类型(Damage/Heal/Buff/Debuff)</t>
+  </si>
+  <si>
+    <t>目标(SingleEnemy/AllEnemies/Self/AllAllies)</t>
+  </si>
+  <si>
+    <t>攻击力倍率</t>
+  </si>
+  <si>
+    <t>附加值(固定数值)</t>
+  </si>
+  <si>
+    <t>Damage</t>
+  </si>
+  <si>
+    <t>SingleEnemy</t>
+  </si>
+  <si>
+    <t>UbSkillId</t>
+  </si>
+  <si>
+    <t>Skill1Id</t>
+  </si>
+  <si>
+    <t>Skill2Id</t>
+  </si>
+  <si>
+    <t>AttackInterval</t>
+  </si>
+  <si>
+    <t>StartSequence</t>
+  </si>
+  <si>
+    <t>LoopSequence</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UB技能id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1技能id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2技能id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>普攻间隔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AA2A1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>准备动画</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>01_idle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>07_idle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>04_idle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>启动序列</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>循环序列</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>猫咪重击</t>
+  </si>
+  <si>
+    <t>猫咪组合拳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>日和莉突击</t>
+  </si>
+  <si>
+    <t>Damage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SingleEnemy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100101_skill0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100101_skill1</t>
+  </si>
+  <si>
+    <t>100101_skill2</t>
+  </si>
+  <si>
+    <t>AA2A1AA1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>全体治愈</t>
+  </si>
+  <si>
+    <t>花瓣射击</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>花之庇护</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100201_skill0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100201_skill1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100201_skill2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpineId</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Spine地址</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>spine_1001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>spine_1002</t>
+  </si>
+  <si>
+    <t>spine_1003</t>
+  </si>
+  <si>
+    <t>spine_1010</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>spine_1036</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>普攻音效地址</t>
+  </si>
+  <si>
+    <t>AttackSound</t>
+  </si>
+  <si>
+    <t>audio_1001_attack</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio_1002_attack</t>
+  </si>
+  <si>
+    <t>audio_1003_attack</t>
+  </si>
+  <si>
+    <t>前摇时长</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio_1001_ub</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio_1001_skill1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio_1001_skill2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio_1002_ub</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio_1002_skill1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio_1002_skill2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AA1A2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100301_skill0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100301_skill1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100301_skill2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio_1003_ub</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio_1003_skill1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio_1003_skill2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>狂风突刺</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>反击斩</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>斩刃风暴</t>
+  </si>
+  <si>
+    <t>OriginName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中文名</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>名称</t>
-  </si>
-  <si>
-    <t>最大HP</t>
-  </si>
-  <si>
-    <t>攻击力</t>
-  </si>
-  <si>
-    <t>攻击范围</t>
-  </si>
-  <si>
-    <t>开局跑步动画</t>
-  </si>
-  <si>
-    <t>跑步动画</t>
-  </si>
-  <si>
-    <t>攻击动画</t>
-  </si>
-  <si>
-    <t>待机动画</t>
-  </si>
-  <si>
-    <t>日和莉</t>
-  </si>
-  <si>
-    <t>01_run_gamestart</t>
-  </si>
-  <si>
-    <t>01_standBy</t>
-  </si>
-  <si>
-    <t>01_run</t>
-  </si>
-  <si>
-    <t>01_attack</t>
-  </si>
-  <si>
-    <t>优衣</t>
-  </si>
-  <si>
-    <t>07_run_gamestart</t>
-  </si>
-  <si>
-    <t>07_standBy</t>
-  </si>
-  <si>
-    <t>07_run</t>
-  </si>
-  <si>
-    <t>07_attack</t>
-  </si>
-  <si>
-    <t>怜</t>
-  </si>
-  <si>
-    <t>04_run_gamestart</t>
-  </si>
-  <si>
-    <t>04_standBy</t>
-  </si>
-  <si>
-    <t>04_run</t>
-  </si>
-  <si>
-    <t>04_attack</t>
-  </si>
-  <si>
-    <t>真步</t>
-  </si>
-  <si>
-    <t>镜华</t>
-  </si>
-  <si>
-    <t>CastTime</t>
-  </si>
-  <si>
-    <t>AnimName</t>
-  </si>
-  <si>
-    <t>SoundName</t>
-  </si>
-  <si>
-    <t>技能ID</t>
-  </si>
-  <si>
-    <t>技能名称</t>
-  </si>
-  <si>
-    <t>技能动画名</t>
-  </si>
-  <si>
-    <t>技能音效名</t>
-  </si>
-  <si>
-    <t>SkillId</t>
-  </si>
-  <si>
-    <t>EffectIndex</t>
-  </si>
-  <si>
-    <t>EffectType</t>
-  </si>
-  <si>
-    <t>EffectTarget</t>
-  </si>
-  <si>
-    <t>SkillMulti</t>
-  </si>
-  <si>
-    <t>EffectValue</t>
-  </si>
-  <si>
-    <t>所属技能ID</t>
-  </si>
-  <si>
-    <t>效果序号(按顺序执行)</t>
-  </si>
-  <si>
-    <t>效果类型(Damage/Heal/Buff/Debuff)</t>
-  </si>
-  <si>
-    <t>目标(SingleEnemy/AllEnemies/Self/AllAllies)</t>
-  </si>
-  <si>
-    <t>攻击力倍率</t>
-  </si>
-  <si>
-    <t>附加值(固定数值)</t>
-  </si>
-  <si>
-    <t>Damage</t>
-  </si>
-  <si>
-    <t>SingleEnemy</t>
-  </si>
-  <si>
-    <t>UbSkillId</t>
-  </si>
-  <si>
-    <t>Skill1Id</t>
-  </si>
-  <si>
-    <t>Skill2Id</t>
-  </si>
-  <si>
-    <t>AttackInterval</t>
-  </si>
-  <si>
-    <t>StartSequence</t>
-  </si>
-  <si>
-    <t>LoopSequence</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>UB技能id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1技能id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2技能id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>普攻间隔</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AA2A1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>准备动画</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>01_idle</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>07_idle</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>04_idle</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>启动序列</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>循环序列</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>猫咪重击</t>
-  </si>
-  <si>
-    <t>猫咪组合拳</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>日和莉突击</t>
-  </si>
-  <si>
-    <t>Damage</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SingleEnemy</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>100101_skill0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>100101_skill1</t>
-  </si>
-  <si>
-    <t>100101_skill2</t>
-  </si>
-  <si>
-    <t>AA2A1AA1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>全体治愈</t>
-  </si>
-  <si>
-    <t>花瓣射击</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>花之庇护</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>100201_skill0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>100201_skill1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>100201_skill2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SpineId</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Spine地址</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>spine_1001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>spine_1002</t>
-  </si>
-  <si>
-    <t>spine_1003</t>
-  </si>
-  <si>
-    <t>spine_1010</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>spine_1036</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>普攻音效地址</t>
-  </si>
-  <si>
-    <t>AttackSound</t>
-  </si>
-  <si>
-    <t>audio_1001_attack</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>audio_1002_attack</t>
-  </si>
-  <si>
-    <t>前摇时长</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>audio_1001_ub</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>audio_1001_skill1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>audio_1001_skill2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>audio_1002_ub</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>audio_1002_skill1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>audio_1002_skill2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hiyori</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Yui</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rei</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Maho</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2AA1A2A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio_1010_ub</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio_1010_skill1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio_1010_skill2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>101001_skill0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>101001_skill1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>101001_skill2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>童话庭院</t>
+  </si>
+  <si>
+    <t>真步真步治愈术</t>
+  </si>
+  <si>
+    <t>真步真步致盲术</t>
+  </si>
+  <si>
+    <t>audio_1010_attack</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -725,7 +837,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R7"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -742,11 +854,11 @@
     <col min="14" max="14" width="16.25" customWidth="1"/>
     <col min="15" max="15" width="15.125" customWidth="1"/>
     <col min="16" max="16" width="19" customWidth="1"/>
-    <col min="17" max="17" width="14.25" customWidth="1"/>
-    <col min="18" max="18" width="13.625" customWidth="1"/>
+    <col min="17" max="17" width="17.75" customWidth="1"/>
+    <col min="18" max="19" width="13.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -754,325 +866,385 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>89</v>
+        <v>118</v>
       </c>
       <c r="D1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1" t="s">
         <v>57</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>58</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>59</v>
       </c>
-      <c r="O1" t="s">
+      <c r="Q1" t="s">
+        <v>96</v>
+      </c>
+      <c r="R1" t="s">
         <v>60</v>
       </c>
-      <c r="P1" t="s">
-        <v>97</v>
-      </c>
-      <c r="Q1" t="s">
+      <c r="S1" t="s">
         <v>61</v>
       </c>
-      <c r="R1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.15">
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>10</v>
       </c>
       <c r="B2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E2" t="s">
         <v>11</v>
       </c>
-      <c r="C2" t="s">
-        <v>90</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>12</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>13</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>14</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
+        <v>67</v>
+      </c>
+      <c r="J2" t="s">
         <v>15</v>
       </c>
-      <c r="H2" t="s">
-        <v>68</v>
-      </c>
-      <c r="I2" t="s">
+      <c r="K2" t="s">
         <v>16</v>
       </c>
-      <c r="J2" t="s">
+      <c r="L2" t="s">
         <v>17</v>
       </c>
-      <c r="K2" t="s">
-        <v>18</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
+        <v>62</v>
+      </c>
+      <c r="N2" t="s">
         <v>63</v>
       </c>
-      <c r="M2" t="s">
+      <c r="O2" t="s">
         <v>64</v>
       </c>
-      <c r="N2" t="s">
+      <c r="P2" t="s">
         <v>65</v>
       </c>
-      <c r="O2" t="s">
-        <v>66</v>
-      </c>
-      <c r="P2" t="s">
-        <v>96</v>
-      </c>
-      <c r="Q2" s="1" t="s">
+      <c r="Q2" t="s">
+        <v>95</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="S2" t="s">
         <v>72</v>
       </c>
-      <c r="R2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.15">
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A3">
         <v>1001</v>
       </c>
       <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E3">
+        <v>5800</v>
+      </c>
+      <c r="F3">
+        <v>1580</v>
+      </c>
+      <c r="G3">
+        <v>200</v>
+      </c>
+      <c r="H3" t="s">
         <v>19</v>
       </c>
-      <c r="C3" t="s">
-        <v>91</v>
-      </c>
-      <c r="D3">
-        <v>5800</v>
-      </c>
-      <c r="E3">
-        <v>1580</v>
-      </c>
-      <c r="F3">
-        <v>200</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="I3" t="s">
         <v>20</v>
       </c>
-      <c r="H3" t="s">
+      <c r="J3" t="s">
         <v>21</v>
       </c>
-      <c r="I3" t="s">
+      <c r="K3" t="s">
         <v>22</v>
       </c>
-      <c r="J3" t="s">
-        <v>23</v>
-      </c>
-      <c r="K3" t="s">
-        <v>69</v>
-      </c>
-      <c r="L3">
+      <c r="L3" t="s">
+        <v>68</v>
+      </c>
+      <c r="M3">
         <v>100100</v>
       </c>
-      <c r="M3">
+      <c r="N3">
         <v>100101</v>
       </c>
-      <c r="N3">
+      <c r="O3">
         <v>100102</v>
       </c>
-      <c r="O3">
+      <c r="P3">
         <v>2.2949999999999999</v>
       </c>
-      <c r="P3" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q3" s="1">
+      <c r="Q3" t="s">
+        <v>97</v>
+      </c>
+      <c r="R3" s="1">
         <v>21</v>
       </c>
-      <c r="R3" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="S3" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A4">
         <v>1002</v>
       </c>
       <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E4">
+        <v>4000</v>
+      </c>
+      <c r="F4">
+        <v>200</v>
+      </c>
+      <c r="G4">
+        <v>800</v>
+      </c>
+      <c r="H4" t="s">
         <v>24</v>
       </c>
-      <c r="C4" t="s">
-        <v>92</v>
-      </c>
-      <c r="D4">
-        <v>4000</v>
-      </c>
-      <c r="E4">
-        <v>200</v>
-      </c>
-      <c r="F4">
-        <v>800</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="I4" t="s">
         <v>25</v>
       </c>
-      <c r="H4" t="s">
+      <c r="J4" t="s">
         <v>26</v>
       </c>
-      <c r="I4" t="s">
+      <c r="K4" t="s">
         <v>27</v>
       </c>
-      <c r="J4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K4" t="s">
-        <v>70</v>
-      </c>
-      <c r="L4">
+      <c r="L4" t="s">
+        <v>69</v>
+      </c>
+      <c r="M4">
         <v>100200</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <v>100201</v>
       </c>
-      <c r="N4">
+      <c r="O4">
         <v>100202</v>
       </c>
-      <c r="O4">
+      <c r="P4">
         <v>2.27</v>
       </c>
-      <c r="P4" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q4" s="1">
+      <c r="Q4" t="s">
+        <v>98</v>
+      </c>
+      <c r="R4" s="1">
         <v>21</v>
       </c>
-      <c r="R4" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="S4" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A5">
         <v>1003</v>
       </c>
       <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D5" t="s">
+        <v>92</v>
+      </c>
+      <c r="E5">
+        <v>5000</v>
+      </c>
+      <c r="F5">
+        <v>1000</v>
+      </c>
+      <c r="G5">
+        <v>250</v>
+      </c>
+      <c r="H5" t="s">
         <v>29</v>
       </c>
-      <c r="C5" t="s">
-        <v>93</v>
-      </c>
-      <c r="D5">
-        <v>5000</v>
-      </c>
-      <c r="E5">
-        <v>1000</v>
-      </c>
-      <c r="F5">
-        <v>250</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="I5" t="s">
         <v>30</v>
       </c>
-      <c r="H5" t="s">
+      <c r="J5" t="s">
         <v>31</v>
       </c>
-      <c r="I5" t="s">
+      <c r="K5" t="s">
         <v>32</v>
       </c>
-      <c r="J5" t="s">
-        <v>33</v>
-      </c>
-      <c r="K5" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="L5" t="s">
+        <v>70</v>
+      </c>
+      <c r="M5">
+        <v>100300</v>
+      </c>
+      <c r="N5">
+        <v>100301</v>
+      </c>
+      <c r="O5">
+        <v>100302</v>
+      </c>
+      <c r="P5">
+        <v>1.9650000000000001</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>99</v>
+      </c>
+      <c r="R5" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="S5" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A6">
         <v>1010</v>
       </c>
       <c r="B6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C6" t="s">
-        <v>94</v>
-      </c>
-      <c r="D6">
-        <v>1000</v>
+        <v>124</v>
+      </c>
+      <c r="D6" t="s">
+        <v>93</v>
       </c>
       <c r="E6">
         <v>1000</v>
       </c>
       <c r="F6">
+        <v>1000</v>
+      </c>
+      <c r="G6">
         <v>795</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I6" t="s">
         <v>25</v>
       </c>
-      <c r="H6" t="s">
+      <c r="J6" t="s">
         <v>26</v>
       </c>
-      <c r="I6" t="s">
+      <c r="K6" t="s">
         <v>27</v>
       </c>
-      <c r="J6" t="s">
-        <v>28</v>
-      </c>
-      <c r="K6" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="L6" t="s">
+        <v>69</v>
+      </c>
+      <c r="M6">
+        <v>101000</v>
+      </c>
+      <c r="N6">
+        <v>101001</v>
+      </c>
+      <c r="O6">
+        <v>101002</v>
+      </c>
+      <c r="P6">
+        <v>2.27</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>135</v>
+      </c>
+      <c r="R6" s="1">
+        <v>21</v>
+      </c>
+      <c r="S6" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A7">
         <v>1036</v>
       </c>
       <c r="B7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C7" t="s">
-        <v>95</v>
-      </c>
-      <c r="D7">
-        <v>1000</v>
+        <v>34</v>
+      </c>
+      <c r="D7" t="s">
+        <v>94</v>
       </c>
       <c r="E7">
         <v>1000</v>
       </c>
       <c r="F7">
+        <v>1000</v>
+      </c>
+      <c r="G7">
         <v>810</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I7" t="s">
         <v>25</v>
       </c>
-      <c r="H7" t="s">
+      <c r="J7" t="s">
         <v>26</v>
       </c>
-      <c r="I7" t="s">
+      <c r="K7" t="s">
         <v>27</v>
       </c>
-      <c r="J7" t="s">
-        <v>28</v>
-      </c>
-      <c r="K7" t="s">
-        <v>70</v>
+      <c r="L7" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -1083,7 +1255,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="4" width="14" customWidth="1"/>
@@ -1099,30 +1271,30 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1" t="s">
         <v>36</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>37</v>
-      </c>
-      <c r="E1" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" t="s">
         <v>39</v>
-      </c>
-      <c r="B2" t="s">
-        <v>40</v>
       </c>
       <c r="C2" t="s">
         <v>100</v>
       </c>
       <c r="D2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E2" t="s">
         <v>41</v>
-      </c>
-      <c r="E2" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.15">
@@ -1130,13 +1302,13 @@
         <v>100100</v>
       </c>
       <c r="B3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E3" t="s">
         <v>101</v>
@@ -1147,13 +1319,13 @@
         <v>100101</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C4">
         <v>1.125</v>
       </c>
       <c r="D4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E4" t="s">
         <v>102</v>
@@ -1164,13 +1336,13 @@
         <v>100102</v>
       </c>
       <c r="B5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C5">
         <v>1.2949999999999999</v>
       </c>
       <c r="D5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E5" t="s">
         <v>103</v>
@@ -1181,13 +1353,13 @@
         <v>100200</v>
       </c>
       <c r="B6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E6" t="s">
         <v>104</v>
@@ -1198,13 +1370,13 @@
         <v>100201</v>
       </c>
       <c r="B7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C7">
         <v>1.6</v>
       </c>
       <c r="D7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E7" t="s">
         <v>105</v>
@@ -1215,16 +1387,118 @@
         <v>100202</v>
       </c>
       <c r="B8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C8">
         <v>1.46</v>
       </c>
       <c r="D8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E8" t="s">
         <v>106</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A9">
+        <v>100300</v>
+      </c>
+      <c r="B9" t="s">
+        <v>117</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9" t="s">
+        <v>109</v>
+      </c>
+      <c r="E9" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A10">
+        <v>100301</v>
+      </c>
+      <c r="B10" t="s">
+        <v>115</v>
+      </c>
+      <c r="C10">
+        <v>0.95499999999999996</v>
+      </c>
+      <c r="D10" t="s">
+        <v>110</v>
+      </c>
+      <c r="E10" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A11">
+        <v>100302</v>
+      </c>
+      <c r="B11" t="s">
+        <v>116</v>
+      </c>
+      <c r="C11">
+        <v>1.3274999999999999</v>
+      </c>
+      <c r="D11" t="s">
+        <v>111</v>
+      </c>
+      <c r="E11" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A12">
+        <v>101000</v>
+      </c>
+      <c r="B12" t="s">
+        <v>132</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12" t="s">
+        <v>129</v>
+      </c>
+      <c r="E12" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A13">
+        <v>101001</v>
+      </c>
+      <c r="B13" t="s">
+        <v>133</v>
+      </c>
+      <c r="C13">
+        <v>0.95499999999999996</v>
+      </c>
+      <c r="D13" t="s">
+        <v>130</v>
+      </c>
+      <c r="E13" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A14">
+        <v>101002</v>
+      </c>
+      <c r="B14" t="s">
+        <v>134</v>
+      </c>
+      <c r="C14">
+        <v>1.3274999999999999</v>
+      </c>
+      <c r="D14" t="s">
+        <v>131</v>
+      </c>
+      <c r="E14" t="s">
+        <v>128</v>
       </c>
     </row>
   </sheetData>
@@ -1248,42 +1522,42 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" t="s">
         <v>43</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>44</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>45</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>46</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>47</v>
-      </c>
-      <c r="F1" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B2" t="s">
         <v>49</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>50</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>51</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>52</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>53</v>
-      </c>
-      <c r="F2" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.15">
@@ -1294,10 +1568,10 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D3" t="s">
         <v>77</v>
-      </c>
-      <c r="D3" t="s">
-        <v>78</v>
       </c>
       <c r="E3">
         <v>2.4</v>
@@ -1314,10 +1588,10 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D4" t="s">
         <v>55</v>
-      </c>
-      <c r="D4" t="s">
-        <v>56</v>
       </c>
       <c r="E4">
         <v>1.6</v>
@@ -1334,10 +1608,10 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D5" t="s">
         <v>55</v>
-      </c>
-      <c r="D5" t="s">
-        <v>56</v>
       </c>
       <c r="E5">
         <v>0.6</v>

--- a/Assets/Configs/CharacterConfig.xlsx
+++ b/Assets/Configs/CharacterConfig.xlsx
@@ -1,28 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\PCR\Assets\Configs\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54C6A7DE-4681-493A-A2F5-B0E265266CBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="25600" windowHeight="12080" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="CharacterConfig" sheetId="1" r:id="rId1"/>
     <sheet name="SkillConfig" sheetId="2" r:id="rId2"/>
     <sheet name="SkillEffectConfig" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="136">
   <si>
     <t>Id</t>
   </si>
@@ -30,6 +37,12 @@
     <t>Name</t>
   </si>
   <si>
+    <t>OriginName</t>
+  </si>
+  <si>
+    <t>SpineId</t>
+  </si>
+  <si>
     <t>MaxHP</t>
   </si>
   <si>
@@ -54,9 +67,39 @@
     <t>AnimIdle</t>
   </si>
   <si>
+    <t>UbSkillId</t>
+  </si>
+  <si>
+    <t>Skill1Id</t>
+  </si>
+  <si>
+    <t>Skill2Id</t>
+  </si>
+  <si>
+    <t>AttackInterval</t>
+  </si>
+  <si>
+    <t>AttackSound</t>
+  </si>
+  <si>
+    <t>StartSequence</t>
+  </si>
+  <si>
+    <t>LoopSequence</t>
+  </si>
+  <si>
     <t>角色ID</t>
   </si>
   <si>
+    <t>中文名</t>
+  </si>
+  <si>
+    <t>名称</t>
+  </si>
+  <si>
+    <t>Spine地址</t>
+  </si>
+  <si>
     <t>最大HP</t>
   </si>
   <si>
@@ -69,6 +112,9 @@
     <t>开局跑步动画</t>
   </si>
   <si>
+    <t>准备动画</t>
+  </si>
+  <si>
     <t>跑步动画</t>
   </si>
   <si>
@@ -78,9 +124,36 @@
     <t>待机动画</t>
   </si>
   <si>
+    <t>UB技能id</t>
+  </si>
+  <si>
+    <t>1技能id</t>
+  </si>
+  <si>
+    <t>2技能id</t>
+  </si>
+  <si>
+    <t>普攻间隔</t>
+  </si>
+  <si>
+    <t>普攻音效地址</t>
+  </si>
+  <si>
+    <t>启动序列</t>
+  </si>
+  <si>
+    <t>循环序列</t>
+  </si>
+  <si>
     <t>日和莉</t>
   </si>
   <si>
+    <t>Hiyori</t>
+  </si>
+  <si>
+    <t>spine_1001</t>
+  </si>
+  <si>
     <t>01_run_gamestart</t>
   </si>
   <si>
@@ -93,9 +166,24 @@
     <t>01_attack</t>
   </si>
   <si>
+    <t>01_idle</t>
+  </si>
+  <si>
+    <t>audio_1001_attack</t>
+  </si>
+  <si>
+    <t>AA2A1</t>
+  </si>
+  <si>
     <t>优衣</t>
   </si>
   <si>
+    <t>Yui</t>
+  </si>
+  <si>
+    <t>spine_1002</t>
+  </si>
+  <si>
     <t>07_run_gamestart</t>
   </si>
   <si>
@@ -108,9 +196,24 @@
     <t>07_attack</t>
   </si>
   <si>
+    <t>07_idle</t>
+  </si>
+  <si>
+    <t>audio_1002_attack</t>
+  </si>
+  <si>
+    <t>AA2A1AA1</t>
+  </si>
+  <si>
     <t>怜</t>
   </si>
   <si>
+    <t>Rei</t>
+  </si>
+  <si>
+    <t>spine_1003</t>
+  </si>
+  <si>
     <t>04_run_gamestart</t>
   </si>
   <si>
@@ -123,12 +226,39 @@
     <t>04_attack</t>
   </si>
   <si>
+    <t>04_idle</t>
+  </si>
+  <si>
+    <t>audio_1003_attack</t>
+  </si>
+  <si>
+    <t>A12</t>
+  </si>
+  <si>
+    <t>AA1A2</t>
+  </si>
+  <si>
     <t>真步</t>
   </si>
   <si>
+    <t>Maho</t>
+  </si>
+  <si>
+    <t>spine_1010</t>
+  </si>
+  <si>
+    <t>audio_1010_attack</t>
+  </si>
+  <si>
+    <t>2AA1A2A</t>
+  </si>
+  <si>
     <t>镜华</t>
   </si>
   <si>
+    <t>spine_1036</t>
+  </si>
+  <si>
     <t>CastTime</t>
   </si>
   <si>
@@ -144,12 +274,123 @@
     <t>技能名称</t>
   </si>
   <si>
+    <t>前摇时长</t>
+  </si>
+  <si>
     <t>技能动画名</t>
   </si>
   <si>
     <t>技能音效名</t>
   </si>
   <si>
+    <t>日和莉突击</t>
+  </si>
+  <si>
+    <t>100101_skill0</t>
+  </si>
+  <si>
+    <t>audio_1001_ub</t>
+  </si>
+  <si>
+    <t>猫咪重击</t>
+  </si>
+  <si>
+    <t>100101_skill1</t>
+  </si>
+  <si>
+    <t>audio_1001_skill1</t>
+  </si>
+  <si>
+    <t>猫咪组合拳</t>
+  </si>
+  <si>
+    <t>100101_skill2</t>
+  </si>
+  <si>
+    <t>audio_1001_skill2</t>
+  </si>
+  <si>
+    <t>全体治愈</t>
+  </si>
+  <si>
+    <t>100201_skill0</t>
+  </si>
+  <si>
+    <t>audio_1002_ub</t>
+  </si>
+  <si>
+    <t>花瓣射击</t>
+  </si>
+  <si>
+    <t>100201_skill1</t>
+  </si>
+  <si>
+    <t>audio_1002_skill1</t>
+  </si>
+  <si>
+    <t>花之庇护</t>
+  </si>
+  <si>
+    <t>100201_skill2</t>
+  </si>
+  <si>
+    <t>audio_1002_skill2</t>
+  </si>
+  <si>
+    <t>斩刃风暴</t>
+  </si>
+  <si>
+    <t>100301_skill0</t>
+  </si>
+  <si>
+    <t>audio_1003_ub</t>
+  </si>
+  <si>
+    <t>狂风突刺</t>
+  </si>
+  <si>
+    <t>100301_skill1</t>
+  </si>
+  <si>
+    <t>audio_1003_skill1</t>
+  </si>
+  <si>
+    <t>反击斩</t>
+  </si>
+  <si>
+    <t>100301_skill2</t>
+  </si>
+  <si>
+    <t>audio_1003_skill2</t>
+  </si>
+  <si>
+    <t>童话庭院</t>
+  </si>
+  <si>
+    <t>101001_skill0</t>
+  </si>
+  <si>
+    <t>audio_1010_ub</t>
+  </si>
+  <si>
+    <t>真步真步治愈术</t>
+  </si>
+  <si>
+    <t>101001_skill1</t>
+  </si>
+  <si>
+    <t>audio_1010_skill1</t>
+  </si>
+  <si>
+    <t>真步真步致盲术</t>
+  </si>
+  <si>
+    <t>101001_skill2</t>
+  </si>
+  <si>
+    <t>audio_1010_skill2</t>
+  </si>
+  <si>
     <t>SkillId</t>
   </si>
   <si>
@@ -168,6 +409,9 @@
     <t>EffectValue</t>
   </si>
   <si>
+    <t>CastFrame</t>
+  </si>
+  <si>
     <t>所属技能ID</t>
   </si>
   <si>
@@ -186,341 +430,373 @@
     <t>附加值(固定数值)</t>
   </si>
   <si>
+    <t>效果前摇</t>
+  </si>
+  <si>
     <t>Damage</t>
   </si>
   <si>
     <t>SingleEnemy</t>
-  </si>
-  <si>
-    <t>UbSkillId</t>
-  </si>
-  <si>
-    <t>Skill1Id</t>
-  </si>
-  <si>
-    <t>Skill2Id</t>
-  </si>
-  <si>
-    <t>AttackInterval</t>
-  </si>
-  <si>
-    <t>StartSequence</t>
-  </si>
-  <si>
-    <t>LoopSequence</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>UB技能id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1技能id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2技能id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>普攻间隔</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AA2A1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>准备动画</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>01_idle</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>07_idle</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>04_idle</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>启动序列</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>循环序列</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>猫咪重击</t>
-  </si>
-  <si>
-    <t>猫咪组合拳</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>日和莉突击</t>
-  </si>
-  <si>
-    <t>Damage</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SingleEnemy</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>100101_skill0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>100101_skill1</t>
-  </si>
-  <si>
-    <t>100101_skill2</t>
-  </si>
-  <si>
-    <t>AA2A1AA1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>全体治愈</t>
-  </si>
-  <si>
-    <t>花瓣射击</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>花之庇护</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>100201_skill0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>100201_skill1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>100201_skill2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SpineId</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Spine地址</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>spine_1001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>spine_1002</t>
-  </si>
-  <si>
-    <t>spine_1003</t>
-  </si>
-  <si>
-    <t>spine_1010</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>spine_1036</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>普攻音效地址</t>
-  </si>
-  <si>
-    <t>AttackSound</t>
-  </si>
-  <si>
-    <t>audio_1001_attack</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>audio_1002_attack</t>
-  </si>
-  <si>
-    <t>audio_1003_attack</t>
-  </si>
-  <si>
-    <t>前摇时长</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>audio_1001_ub</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>audio_1001_skill1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>audio_1001_skill2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>audio_1002_ub</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>audio_1002_skill1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>audio_1002_skill2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>A12</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AA1A2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>100301_skill0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>100301_skill1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>100301_skill2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>audio_1003_ub</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>audio_1003_skill1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>audio_1003_skill2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>狂风突刺</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>反击斩</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>斩刃风暴</t>
-  </si>
-  <si>
-    <t>OriginName</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>中文名</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>名称</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Hiyori</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Yui</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Rei</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Maho</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2AA1A2A</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>audio_1010_ub</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>audio_1010_skill1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>audio_1010_skill2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>101001_skill0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>101001_skill1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>101001_skill2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>童话庭院</t>
-  </si>
-  <si>
-    <t>真步真步治愈术</t>
-  </si>
-  <si>
-    <t>真步真步致盲术</t>
-  </si>
-  <si>
-    <t>audio_1010_attack</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
-      <family val="3"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -528,25 +804,311 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -831,34 +1393,34 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:S7"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="6"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="10.5" customWidth="1"/>
-    <col min="3" max="3" width="12.625" customWidth="1"/>
-    <col min="4" max="5" width="12.75" customWidth="1"/>
-    <col min="6" max="6" width="12.625" customWidth="1"/>
-    <col min="7" max="7" width="18.625" customWidth="1"/>
+    <col min="3" max="3" width="12.6272727272727" customWidth="1"/>
+    <col min="4" max="5" width="12.7545454545455" customWidth="1"/>
+    <col min="6" max="6" width="12.6272727272727" customWidth="1"/>
+    <col min="7" max="7" width="18.6272727272727" customWidth="1"/>
     <col min="8" max="8" width="16" customWidth="1"/>
-    <col min="9" max="9" width="12.625" customWidth="1"/>
-    <col min="10" max="10" width="11.875" customWidth="1"/>
+    <col min="9" max="9" width="12.6272727272727" customWidth="1"/>
+    <col min="10" max="10" width="11.8727272727273" customWidth="1"/>
     <col min="11" max="12" width="16" customWidth="1"/>
     <col min="13" max="13" width="11.5" customWidth="1"/>
-    <col min="14" max="14" width="16.25" customWidth="1"/>
-    <col min="15" max="15" width="15.125" customWidth="1"/>
+    <col min="14" max="14" width="16.2545454545455" customWidth="1"/>
+    <col min="15" max="15" width="15.1272727272727" customWidth="1"/>
     <col min="16" max="16" width="19" customWidth="1"/>
-    <col min="17" max="17" width="17.75" customWidth="1"/>
-    <col min="18" max="19" width="13.625" customWidth="1"/>
+    <col min="17" max="17" width="17.7545454545455" customWidth="1"/>
+    <col min="18" max="19" width="13.6272727272727" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:19">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -866,128 +1428,128 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>118</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>88</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M1" t="s">
-        <v>56</v>
+        <v>12</v>
       </c>
       <c r="N1" t="s">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="O1" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="P1" t="s">
-        <v>59</v>
+        <v>15</v>
       </c>
       <c r="Q1" t="s">
-        <v>96</v>
+        <v>16</v>
       </c>
       <c r="R1" t="s">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="S1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.15">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>119</v>
+        <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>120</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>89</v>
+        <v>22</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="H2" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="I2" t="s">
-        <v>67</v>
+        <v>27</v>
       </c>
       <c r="J2" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="K2" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="L2" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="M2" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="N2" t="s">
-        <v>63</v>
+        <v>32</v>
       </c>
       <c r="O2" t="s">
-        <v>64</v>
+        <v>33</v>
       </c>
       <c r="P2" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="Q2" t="s">
-        <v>95</v>
+        <v>35</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>71</v>
+        <v>36</v>
       </c>
       <c r="S2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.15">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19">
       <c r="A3">
         <v>1001</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="C3" t="s">
-        <v>121</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="E3">
         <v>5800</v>
@@ -999,19 +1561,19 @@
         <v>200</v>
       </c>
       <c r="H3" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="I3" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="J3" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="K3" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="L3" t="s">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="M3">
         <v>100100</v>
@@ -1023,30 +1585,30 @@
         <v>100102</v>
       </c>
       <c r="P3">
-        <v>2.2949999999999999</v>
+        <v>2.295</v>
       </c>
       <c r="Q3" t="s">
-        <v>97</v>
+        <v>46</v>
       </c>
       <c r="R3" s="1">
         <v>21</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.15">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19">
       <c r="A4">
         <v>1002</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="C4" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="D4" t="s">
-        <v>91</v>
+        <v>50</v>
       </c>
       <c r="E4">
         <v>4000</v>
@@ -1058,19 +1620,19 @@
         <v>800</v>
       </c>
       <c r="H4" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="I4" t="s">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="J4" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="K4" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="L4" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="M4">
         <v>100200</v>
@@ -1085,27 +1647,27 @@
         <v>2.27</v>
       </c>
       <c r="Q4" t="s">
-        <v>98</v>
+        <v>56</v>
       </c>
       <c r="R4" s="1">
         <v>21</v>
       </c>
       <c r="S4" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.15">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19">
       <c r="A5">
         <v>1003</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="C5" t="s">
-        <v>123</v>
+        <v>59</v>
       </c>
       <c r="D5" t="s">
-        <v>92</v>
+        <v>60</v>
       </c>
       <c r="E5">
         <v>5000</v>
@@ -1117,19 +1679,19 @@
         <v>250</v>
       </c>
       <c r="H5" t="s">
-        <v>29</v>
+        <v>61</v>
       </c>
       <c r="I5" t="s">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="J5" t="s">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="K5" t="s">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="L5" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="M5">
         <v>100300</v>
@@ -1141,30 +1703,30 @@
         <v>100302</v>
       </c>
       <c r="P5">
-        <v>1.9650000000000001</v>
+        <v>1.965</v>
       </c>
       <c r="Q5" t="s">
-        <v>99</v>
+        <v>66</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>107</v>
+        <v>67</v>
       </c>
       <c r="S5" s="1" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.15">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19">
       <c r="A6">
         <v>1010</v>
       </c>
       <c r="B6" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>124</v>
+        <v>70</v>
       </c>
       <c r="D6" t="s">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="E6">
         <v>1000</v>
@@ -1176,19 +1738,19 @@
         <v>795</v>
       </c>
       <c r="H6" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="I6" t="s">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="J6" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="K6" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="L6" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="M6">
         <v>101000</v>
@@ -1203,24 +1765,24 @@
         <v>2.27</v>
       </c>
       <c r="Q6" t="s">
-        <v>135</v>
+        <v>72</v>
       </c>
       <c r="R6" s="1">
         <v>21</v>
       </c>
       <c r="S6" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.15">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19">
       <c r="A7">
         <v>1036</v>
       </c>
       <c r="B7" t="s">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="D7" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="E7">
         <v>1000</v>
@@ -1232,38 +1794,39 @@
         <v>810</v>
       </c>
       <c r="H7" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="I7" t="s">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="J7" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="K7" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="L7" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:E14"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="17.75" customWidth="1"/>
+    <col min="5" max="5" width="17.7545454545455" customWidth="1"/>
     <col min="6" max="9" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1271,296 +1834,304 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>35</v>
+        <v>76</v>
       </c>
       <c r="D1" t="s">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="E1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="B2" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="C2" t="s">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>82</v>
       </c>
       <c r="E2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>100100</v>
       </c>
       <c r="B3" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="E3" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4">
         <v>100101</v>
       </c>
       <c r="B4" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="C4">
         <v>1.125</v>
       </c>
       <c r="D4" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="E4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5">
         <v>100102</v>
       </c>
       <c r="B5" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="C5">
-        <v>1.2949999999999999</v>
+        <v>1.295</v>
       </c>
       <c r="D5" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="E5" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.15">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6">
         <v>100200</v>
       </c>
       <c r="B6" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="E6" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.15">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7">
         <v>100201</v>
       </c>
       <c r="B7" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="C7">
         <v>1.6</v>
       </c>
       <c r="D7" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="E7" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.15">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8">
         <v>100202</v>
       </c>
       <c r="B8" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="C8">
         <v>1.46</v>
       </c>
       <c r="D8" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="E8" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.15">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9">
         <v>100300</v>
       </c>
       <c r="B9" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="E9" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.15">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10">
         <v>100301</v>
       </c>
       <c r="B10" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="C10">
-        <v>0.95499999999999996</v>
+        <v>0.955</v>
       </c>
       <c r="D10" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E10" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.15">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11">
         <v>100302</v>
       </c>
       <c r="B11" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="C11">
-        <v>1.3274999999999999</v>
+        <v>1.3275</v>
       </c>
       <c r="D11" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E11" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.15">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12">
         <v>101000</v>
       </c>
       <c r="B12" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12" t="s">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="E12" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.15">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13">
         <v>101001</v>
       </c>
       <c r="B13" t="s">
-        <v>133</v>
+        <v>114</v>
       </c>
       <c r="C13">
-        <v>0.95499999999999996</v>
+        <v>0.955</v>
       </c>
       <c r="D13" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="E13" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.15">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
       <c r="A14">
         <v>101002</v>
       </c>
       <c r="B14" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="C14">
-        <v>1.3274999999999999</v>
+        <v>1.3275</v>
       </c>
       <c r="D14" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="E14" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="6" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="20.875" customWidth="1"/>
-    <col min="3" max="3" width="32.875" customWidth="1"/>
-    <col min="4" max="4" width="44.75" customWidth="1"/>
+    <col min="2" max="2" width="20.8727272727273" customWidth="1"/>
+    <col min="3" max="3" width="32.8727272727273" customWidth="1"/>
+    <col min="4" max="4" width="44.7545454545455" customWidth="1"/>
     <col min="5" max="5" width="12.5" customWidth="1"/>
-    <col min="6" max="6" width="18.25" customWidth="1"/>
+    <col min="6" max="6" width="18.2545454545455" customWidth="1"/>
+    <col min="7" max="7" width="11.2181818181818" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>42</v>
+        <v>120</v>
       </c>
       <c r="B1" t="s">
-        <v>43</v>
+        <v>121</v>
       </c>
       <c r="C1" t="s">
-        <v>44</v>
+        <v>122</v>
       </c>
       <c r="D1" t="s">
-        <v>45</v>
+        <v>123</v>
       </c>
       <c r="E1" t="s">
-        <v>46</v>
+        <v>124</v>
       </c>
       <c r="F1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.15">
+        <v>125</v>
+      </c>
+      <c r="G1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>48</v>
+        <v>127</v>
       </c>
       <c r="B2" t="s">
-        <v>49</v>
+        <v>128</v>
       </c>
       <c r="C2" t="s">
-        <v>50</v>
+        <v>129</v>
       </c>
       <c r="D2" t="s">
-        <v>51</v>
+        <v>130</v>
       </c>
       <c r="E2" t="s">
-        <v>52</v>
+        <v>131</v>
       </c>
       <c r="F2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.15">
+        <v>132</v>
+      </c>
+      <c r="G2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>100100</v>
       </c>
@@ -1568,10 +2139,10 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>76</v>
+        <v>134</v>
       </c>
       <c r="D3" t="s">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="E3">
         <v>2.4</v>
@@ -1580,7 +2151,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:7">
       <c r="A4">
         <v>100101</v>
       </c>
@@ -1588,10 +2159,10 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>54</v>
+        <v>134</v>
       </c>
       <c r="D4" t="s">
-        <v>55</v>
+        <v>135</v>
       </c>
       <c r="E4">
         <v>1.6</v>
@@ -1599,8 +2170,11 @@
       <c r="F4">
         <v>20</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>100102</v>
       </c>
@@ -1608,10 +2182,10 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>54</v>
+        <v>134</v>
       </c>
       <c r="D5" t="s">
-        <v>55</v>
+        <v>135</v>
       </c>
       <c r="E5">
         <v>0.6</v>
@@ -1619,9 +2193,58 @@
       <c r="F5">
         <v>8</v>
       </c>
+      <c r="G5">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>100102</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6" t="s">
+        <v>134</v>
+      </c>
+      <c r="D6" t="s">
+        <v>135</v>
+      </c>
+      <c r="E6">
+        <v>0.6</v>
+      </c>
+      <c r="F6">
+        <v>8</v>
+      </c>
+      <c r="G6">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>100102</v>
+      </c>
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7" t="s">
+        <v>134</v>
+      </c>
+      <c r="D7" t="s">
+        <v>135</v>
+      </c>
+      <c r="E7">
+        <v>0.6</v>
+      </c>
+      <c r="F7">
+        <v>8</v>
+      </c>
+      <c r="G7">
+        <v>74</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/Configs/CharacterConfig.xlsx
+++ b/Assets/Configs/CharacterConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\PCR\Assets\Configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{857EF917-1920-4261-A6EB-9EED80664A73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{027D93AC-F9A2-498B-8892-5822AE43A1DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CharacterConfig" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="154">
   <si>
     <t>Id</t>
   </si>
@@ -136,9 +136,6 @@
     <t>01_idle</t>
   </si>
   <si>
-    <t>audio_1001_attack</t>
-  </si>
-  <si>
     <t>AA2A1</t>
   </si>
   <si>
@@ -166,9 +163,6 @@
     <t>07_idle</t>
   </si>
   <si>
-    <t>audio_1002_attack</t>
-  </si>
-  <si>
     <t>AA2A1AA1</t>
   </si>
   <si>
@@ -250,108 +244,72 @@
     <t>100101_skill0</t>
   </si>
   <si>
-    <t>audio_1001_ub</t>
-  </si>
-  <si>
     <t>猫咪重击</t>
   </si>
   <si>
     <t>100101_skill1</t>
   </si>
   <si>
-    <t>audio_1001_skill1</t>
-  </si>
-  <si>
     <t>猫咪组合拳</t>
   </si>
   <si>
     <t>100101_skill2</t>
   </si>
   <si>
-    <t>audio_1001_skill2</t>
-  </si>
-  <si>
     <t>全体治愈</t>
   </si>
   <si>
     <t>100201_skill0</t>
   </si>
   <si>
-    <t>audio_1002_ub</t>
-  </si>
-  <si>
     <t>花瓣射击</t>
   </si>
   <si>
     <t>100201_skill1</t>
   </si>
   <si>
-    <t>audio_1002_skill1</t>
-  </si>
-  <si>
     <t>花之庇护</t>
   </si>
   <si>
     <t>100201_skill2</t>
   </si>
   <si>
-    <t>audio_1002_skill2</t>
-  </si>
-  <si>
     <t>斩刃风暴</t>
   </si>
   <si>
     <t>100301_skill0</t>
   </si>
   <si>
-    <t>audio_1003_ub</t>
-  </si>
-  <si>
     <t>狂风突刺</t>
   </si>
   <si>
     <t>100301_skill1</t>
   </si>
   <si>
-    <t>audio_1003_skill1</t>
-  </si>
-  <si>
     <t>反击斩</t>
   </si>
   <si>
     <t>100301_skill2</t>
   </si>
   <si>
-    <t>audio_1003_skill2</t>
-  </si>
-  <si>
     <t>童话庭院</t>
   </si>
   <si>
     <t>101001_skill0</t>
   </si>
   <si>
-    <t>audio_1010_ub</t>
-  </si>
-  <si>
     <t>真步真步治愈术</t>
   </si>
   <si>
     <t>101001_skill1</t>
   </si>
   <si>
-    <t>audio_1010_skill1</t>
-  </si>
-  <si>
     <t>真步真步致盲术</t>
   </si>
   <si>
     <t>101001_skill2</t>
   </si>
   <si>
-    <t>audio_1010_skill2</t>
-  </si>
-  <si>
     <t>SkillId</t>
   </si>
   <si>
@@ -406,14 +364,6 @@
   </si>
   <si>
     <t>CharacterId</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>audio_1003_attack</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>audio_1010_attack</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -440,21 +390,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>PhysicalAttack</t>
-  </si>
-  <si>
-    <t>物理攻击</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>魔法攻击</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>生命值</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>DamageType</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -521,14 +456,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>HP</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>MagicAttack</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>100201_attack</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -550,6 +477,70 @@
   </si>
   <si>
     <t>101001_attack</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vo_btl_100101_attack_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vo_btl_100101_ub_200</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vo_btl_100101_skill_100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vo_btl_100101_skill_200</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vo_btl_100201_skill_100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vo_btl_100201_skill_200</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vo_btl_100201_attack_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vo_btl_100201_ub_200</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vo_btl_100301_attack_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vo_btl_100301_ub_200</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vo_btl_100301_skill_100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vo_btl_100301_skill_200</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vo_btl_101001_attack_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vo_btl_101001_ub_200</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vo_btl_101001_skill_100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vo_btl_101001_skill_200</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -917,7 +908,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R7"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -938,7 +929,7 @@
     <col min="18" max="19" width="13.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -951,50 +942,41 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>152</v>
+      <c r="E1" t="s">
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>131</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>153</v>
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>6</v>
+        <v>109</v>
       </c>
       <c r="K1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M1" t="s">
-        <v>125</v>
+        <v>11</v>
       </c>
       <c r="N1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="O1" t="s">
-        <v>10</v>
-      </c>
-      <c r="P1" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>12</v>
-      </c>
-      <c r="R1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -1007,50 +989,41 @@
       <c r="D2" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>133</v>
+      <c r="E2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s">
+        <v>20</v>
       </c>
       <c r="H2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J2" t="s">
-        <v>20</v>
-      </c>
-      <c r="K2" t="s">
-        <v>21</v>
-      </c>
-      <c r="L2" t="s">
         <v>22</v>
       </c>
+      <c r="J2" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>112</v>
+      </c>
       <c r="M2" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="Q2" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="R2" t="s">
+      <c r="O2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A3">
         <v>1001</v>
       </c>
@@ -1064,249 +1037,204 @@
         <v>27</v>
       </c>
       <c r="E3">
-        <v>5800</v>
-      </c>
-      <c r="F3">
-        <v>1580</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
         <v>200</v>
       </c>
+      <c r="F3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H3" t="s">
+        <v>30</v>
+      </c>
       <c r="I3" t="s">
-        <v>28</v>
-      </c>
-      <c r="J3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L3" t="s">
         <v>32</v>
       </c>
-      <c r="M3" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="O3" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="P3" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q3" s="1">
+      <c r="J3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="N3" s="1">
         <v>21</v>
       </c>
-      <c r="R3" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="O3" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A4">
         <v>1002</v>
       </c>
       <c r="B4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" t="s">
         <v>35</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>36</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4">
+        <v>800</v>
+      </c>
+      <c r="F4" t="s">
         <v>37</v>
       </c>
-      <c r="E4">
-        <v>4000</v>
-      </c>
-      <c r="F4">
-        <v>200</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>800</v>
+      <c r="G4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H4" t="s">
+        <v>39</v>
       </c>
       <c r="I4" t="s">
-        <v>38</v>
-      </c>
-      <c r="J4" t="s">
-        <v>39</v>
-      </c>
-      <c r="K4" t="s">
-        <v>40</v>
-      </c>
-      <c r="L4" t="s">
+        <v>41</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="N4" s="1">
+        <v>21</v>
+      </c>
+      <c r="O4" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="M4" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="O4" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="P4" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="Q4" s="1">
-        <v>21</v>
-      </c>
-      <c r="R4" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.15">
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A5">
         <v>1003</v>
       </c>
       <c r="B5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D5" t="s">
         <v>45</v>
       </c>
-      <c r="C5" t="s">
+      <c r="E5">
+        <v>250</v>
+      </c>
+      <c r="F5" t="s">
         <v>46</v>
       </c>
-      <c r="D5" t="s">
+      <c r="G5" t="s">
         <v>47</v>
       </c>
-      <c r="E5">
-        <v>5000</v>
-      </c>
-      <c r="F5">
-        <v>1000</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>250</v>
+      <c r="H5" t="s">
+        <v>48</v>
       </c>
       <c r="I5" t="s">
-        <v>48</v>
-      </c>
-      <c r="J5" t="s">
-        <v>49</v>
-      </c>
-      <c r="K5" t="s">
         <v>50</v>
       </c>
-      <c r="L5" t="s">
+      <c r="J5" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="O5" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="M5" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="N5" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="O5" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="P5" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="Q5" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="R5" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.15">
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A6">
         <v>1010</v>
       </c>
       <c r="B6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D6" t="s">
         <v>55</v>
       </c>
-      <c r="C6" t="s">
+      <c r="E6">
+        <v>795</v>
+      </c>
+      <c r="F6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H6" t="s">
+        <v>39</v>
+      </c>
+      <c r="I6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="L6" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="M6" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="N6" s="1">
+        <v>21</v>
+      </c>
+      <c r="O6" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D6" t="s">
-        <v>57</v>
-      </c>
-      <c r="E6">
-        <v>1000</v>
-      </c>
-      <c r="F6">
-        <v>1000</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>795</v>
-      </c>
-      <c r="I6" t="s">
-        <v>38</v>
-      </c>
-      <c r="J6" t="s">
-        <v>39</v>
-      </c>
-      <c r="K6" t="s">
-        <v>40</v>
-      </c>
-      <c r="L6" t="s">
-        <v>42</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="N6" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="O6" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="P6" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="Q6" s="1">
-        <v>21</v>
-      </c>
-      <c r="R6" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.15">
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A7">
         <v>1036</v>
       </c>
       <c r="B7" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D7" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E7">
-        <v>1000</v>
-      </c>
-      <c r="F7">
-        <v>1000</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
         <v>810</v>
       </c>
+      <c r="F7" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7" t="s">
+        <v>38</v>
+      </c>
+      <c r="H7" t="s">
+        <v>39</v>
+      </c>
       <c r="I7" t="s">
-        <v>38</v>
-      </c>
-      <c r="J7" t="s">
-        <v>39</v>
-      </c>
-      <c r="K7" t="s">
-        <v>40</v>
-      </c>
-      <c r="L7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1324,13 +1252,13 @@
     <col min="2" max="2" width="15.625" customWidth="1"/>
     <col min="3" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="17.75" customWidth="1"/>
-    <col min="6" max="6" width="18.375" customWidth="1"/>
+    <col min="6" max="6" width="26.5" customWidth="1"/>
     <col min="7" max="9" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -1339,33 +1267,33 @@
         <v>1</v>
       </c>
       <c r="D1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F1" t="s">
         <v>61</v>
-      </c>
-      <c r="E1" t="s">
-        <v>62</v>
-      </c>
-      <c r="F1" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="B2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2" t="s">
         <v>64</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>65</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>66</v>
-      </c>
-      <c r="E2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F2" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.15">
@@ -1373,10 +1301,10 @@
         <v>1001</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="D3">
         <v>2.2949999999999999</v>
@@ -1384,62 +1312,62 @@
       <c r="E3" t="s">
         <v>31</v>
       </c>
-      <c r="F3" t="s">
-        <v>33</v>
+      <c r="F3" s="2" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A4" s="3"/>
       <c r="B4" s="4" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4" t="s">
-        <v>70</v>
-      </c>
-      <c r="F4" t="s">
-        <v>71</v>
+        <v>68</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A5" s="3"/>
       <c r="B5" s="4" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D5">
         <v>1.125</v>
       </c>
       <c r="E5" t="s">
-        <v>73</v>
-      </c>
-      <c r="F5" t="s">
-        <v>74</v>
+        <v>70</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A6" s="3"/>
       <c r="B6" s="4" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C6" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D6">
         <v>1.2949999999999999</v>
       </c>
       <c r="E6" t="s">
-        <v>76</v>
-      </c>
-      <c r="F6" t="s">
-        <v>77</v>
+        <v>72</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.15">
@@ -1447,73 +1375,73 @@
         <v>1002</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="D7">
         <v>2.27</v>
       </c>
       <c r="E7" t="s">
-        <v>41</v>
-      </c>
-      <c r="F7" t="s">
-        <v>43</v>
+        <v>40</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A8" s="3"/>
       <c r="B8" s="4" t="s">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="C8" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8" t="s">
-        <v>79</v>
-      </c>
-      <c r="F8" t="s">
-        <v>80</v>
+        <v>74</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A9" s="3"/>
       <c r="B9" s="4" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C9" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="D9">
         <v>1.6</v>
       </c>
       <c r="E9" t="s">
-        <v>82</v>
-      </c>
-      <c r="F9" t="s">
-        <v>83</v>
+        <v>76</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A10" s="3"/>
       <c r="B10" s="4" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="C10" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="D10">
         <v>1.46</v>
       </c>
       <c r="E10" t="s">
-        <v>85</v>
-      </c>
-      <c r="F10" t="s">
-        <v>86</v>
+        <v>78</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.15">
@@ -1521,73 +1449,73 @@
         <v>1003</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>145</v>
+        <v>125</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="D11">
         <v>1.9650000000000001</v>
       </c>
       <c r="E11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>123</v>
+        <v>146</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A12" s="3"/>
       <c r="B12" s="4" t="s">
-        <v>146</v>
+        <v>126</v>
       </c>
       <c r="C12" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="D12">
         <v>0</v>
       </c>
       <c r="E12" t="s">
-        <v>88</v>
-      </c>
-      <c r="F12" t="s">
-        <v>89</v>
+        <v>80</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A13" s="3"/>
       <c r="B13" s="4" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="C13" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="D13">
         <v>0.95499999999999996</v>
       </c>
       <c r="E13" t="s">
-        <v>91</v>
-      </c>
-      <c r="F13" t="s">
-        <v>92</v>
+        <v>82</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A14" s="3"/>
       <c r="B14" s="4" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="C14" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="D14">
         <v>1.3274999999999999</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="F14" t="s">
-        <v>95</v>
+        <v>120</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.15">
@@ -1595,73 +1523,73 @@
         <v>1010</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>159</v>
+        <v>137</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="D15">
         <v>2.27</v>
       </c>
       <c r="E15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>124</v>
+        <v>150</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A16" s="3"/>
       <c r="B16" s="4" t="s">
-        <v>147</v>
+        <v>127</v>
       </c>
       <c r="C16" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="D16">
         <v>0</v>
       </c>
       <c r="E16" t="s">
-        <v>97</v>
-      </c>
-      <c r="F16" t="s">
-        <v>98</v>
+        <v>86</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A17" s="3"/>
       <c r="B17" s="4" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="C17" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="D17">
         <v>0.95499999999999996</v>
       </c>
       <c r="E17" t="s">
-        <v>100</v>
-      </c>
-      <c r="F17" t="s">
-        <v>101</v>
+        <v>88</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A18" s="3"/>
       <c r="B18" s="4" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="C18" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="D18">
         <v>1.3274999999999999</v>
       </c>
       <c r="E18" t="s">
-        <v>103</v>
-      </c>
-      <c r="F18" t="s">
-        <v>104</v>
+        <v>90</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>153</v>
       </c>
     </row>
   </sheetData>
@@ -1694,77 +1622,83 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="B1" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="C1" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="D1" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="F1" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="G1" t="s">
-        <v>137</v>
+        <v>117</v>
       </c>
       <c r="H1" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="I1" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="B2" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="C2" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="D2" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>136</v>
+        <v>116</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>139</v>
+        <v>119</v>
       </c>
       <c r="G2" t="s">
-        <v>138</v>
+        <v>118</v>
       </c>
       <c r="H2" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="I2" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="D3" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>151</v>
+        <v>131</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
       </c>
       <c r="H3">
         <v>1</v>
@@ -1775,19 +1709,19 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A4" s="4" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="D4" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="F4">
         <v>30</v>
@@ -1801,19 +1735,19 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A5" s="4" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="D5" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="F5">
         <v>20</v>
@@ -1830,23 +1764,26 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A6" s="4" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="D6" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="F6">
         <v>8</v>
       </c>
+      <c r="G6">
+        <v>8</v>
+      </c>
       <c r="H6">
         <v>0.6</v>
       </c>
@@ -1856,23 +1793,26 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A7" s="4" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="B7">
         <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="D7" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="F7">
         <v>8</v>
       </c>
+      <c r="G7">
+        <v>8</v>
+      </c>
       <c r="H7">
         <v>0.6</v>
       </c>
@@ -1882,23 +1822,26 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A8" s="4" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="B8">
         <v>3</v>
       </c>
       <c r="C8" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="D8" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="F8">
         <v>8</v>
       </c>
+      <c r="G8">
+        <v>8</v>
+      </c>
       <c r="H8">
         <v>0.6</v>
       </c>
@@ -1908,19 +1851,25 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A9" s="2" t="s">
-        <v>145</v>
+        <v>125</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="D9" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>151</v>
+        <v>131</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -1931,46 +1880,52 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A10" s="2" t="s">
-        <v>146</v>
+        <v>126</v>
       </c>
       <c r="B10">
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="D10" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="F10">
-        <v>30</v>
+        <v>60</v>
+      </c>
+      <c r="G10">
+        <v>60</v>
       </c>
       <c r="H10">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A11" s="2" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="B11">
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="D11" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="F11">
         <v>20</v>
       </c>
+      <c r="G11">
+        <v>20</v>
+      </c>
       <c r="H11">
         <v>1.6</v>
       </c>
@@ -1980,25 +1935,28 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A12" s="2" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="B12">
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="D12" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="F12">
-        <v>8</v>
+        <v>20</v>
+      </c>
+      <c r="G12">
+        <v>20</v>
       </c>
       <c r="H12">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="I12">
         <v>24</v>
